--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T21:42:02+08:00</t>
+    <t>2026-07-10T19:56:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T19:56:53+08:00</t>
+    <t>2026-07-10T21:30:50+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T21:30:50+08:00</t>
+    <t>2026-07-23T22:22:27+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -115,6 +115,12 @@
   </si>
   <si>
     <t>Body weight</t>
+  </si>
+  <si>
+    <t>8280-0</t>
+  </si>
+  <si>
+    <t>Waist Circumference at umbilicus by Tape measure</t>
   </si>
   <si>
     <t>56086-2</t>
@@ -422,7 +428,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -495,18 +501,26 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>22</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>45</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-23T22:22:27+08:00</t>
+    <t>2026-07-24T13:54:16+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-24T13:54:16+08:00</t>
+    <t>2026-07-25T16:18:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -126,7 +126,7 @@
     <t>56086-2</t>
   </si>
   <si>
-    <t>Waist Circumference</t>
+    <t>Adult Waist Circumference Protocol</t>
   </si>
   <si>
     <t>8480-6</t>
@@ -145,12 +145,6 @@
   </si>
   <si>
     <t>Body mass index (BMI) [Ratio]</t>
-  </si>
-  <si>
-    <t>73708-3</t>
-  </si>
-  <si>
-    <t>Waist-to-hip ratio</t>
   </si>
   <si>
     <t>System URI</t>
@@ -428,7 +422,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -501,26 +495,18 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>45</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s" s="2">
-        <v>46</v>
-      </c>
-      <c r="B11" t="s" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-25T16:18:15+08:00</t>
+    <t>2026-07-26T10:07:44+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -121,12 +121,6 @@
   </si>
   <si>
     <t>Waist Circumference at umbilicus by Tape measure</t>
-  </si>
-  <si>
-    <t>56086-2</t>
-  </si>
-  <si>
-    <t>Adult Waist Circumference Protocol</t>
   </si>
   <si>
     <t>8480-6</t>
@@ -422,7 +416,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -487,26 +481,18 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>43</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s" s="2">
-        <v>44</v>
-      </c>
-      <c r="B10" t="s" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T10:07:44+08:00</t>
+    <t>2026-07-26T12:18:37+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T12:18:37+08:00</t>
+    <t>2026-07-26T14:28:30+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T14:28:30+08:00</t>
+    <t>2026-07-26T15:21:49+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T15:21:49+08:00</t>
+    <t>2026-07-26T16:11:18+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T16:11:18+08:00</t>
+    <t>2026-07-26T18:45:10+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-26T18:45:10+08:00</t>
+    <t>2026-07-29T09:46:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T09:46:30+00:00</t>
+    <t>2026-07-29T14:03:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T14:03:51+00:00</t>
+    <t>2026-07-29T16:26:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:26:07+00:00</t>
+    <t>2026-07-29T16:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T16:54:28+00:00</t>
+    <t>2026-07-30T07:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -111,10 +111,22 @@
     <t>Body height</t>
   </si>
   <si>
+    <t>3137-7</t>
+  </si>
+  <si>
+    <t>Body height Measured</t>
+  </si>
+  <si>
     <t>29463-7</t>
   </si>
   <si>
     <t>Body weight</t>
+  </si>
+  <si>
+    <t>3141-9</t>
+  </si>
+  <si>
+    <t>Body weight Measured</t>
   </si>
   <si>
     <t>8280-0</t>
@@ -416,7 +428,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -481,18 +493,34 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>22</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>43</v>
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="2">
+        <v>46</v>
+      </c>
+      <c r="B11" t="s" s="2">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T07:25:13+00:00</t>
+    <t>2026-07-30T09:28:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T09:28:37+00:00</t>
+    <t>2026-07-30T10:44:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T10:44:37+00:00</t>
+    <t>2026-07-30T12:17:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T12:17:12+00:00</t>
+    <t>2026-07-30T14:17:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:17:56+00:00</t>
+    <t>2026-07-30T14:46:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T14:46:31+00:00</t>
+    <t>2026-08-05T16:28:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>0.2.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:28:11+00:00</t>
+    <t>2026-08-05T16:48:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.1</t>
+    <t>0.2.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-05T16:48:01+00:00</t>
+    <t>2026-08-17T03:02:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.3</t>
+    <t>0.2.4</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T03:02:16+00:00</t>
+    <t>2026-08-17T05:27:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.4</t>
+    <t>0.2.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T05:27:05+00:00</t>
+    <t>2026-08-17T06:57:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.5</t>
+    <t>0.3.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-17T06:57:01+00:00</t>
+    <t>2026-08-20T12:04:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.3</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T12:04:33+00:00</t>
+    <t>2026-08-20T13:40:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T13:40:11+00:00</t>
+    <t>2026-08-20T16:35:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>包含身高、體重、腰圍及血壓等生理測量項目之 LOINC 代碼。</t>
+    <t>【主管機關：國民健康署】包含身高、體重、腰圍及血壓等生理測量項目之 LOINC 代碼。</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T16:35:38+00:00</t>
+    <t>2026-08-20T17:39:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T17:39:23+00:00</t>
+    <t>2026-08-20T18:13:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.1</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-20T18:13:29+00:00</t>
+    <t>2026-08-21T00:14:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:14:56+00:00</t>
+    <t>2026-08-21T00:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.7.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T00:59:40+00:00</t>
+    <t>2026-08-21T01:22:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.1</t>
+    <t>0.8.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T01:22:55+00:00</t>
+    <t>2026-08-21T04:20:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.1</t>
+    <t>0.8.5</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T04:20:36+00:00</t>
+    <t>2026-08-21T12:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.8.5</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T12:32:47+00:00</t>
+    <t>2026-08-21T14:27:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.9.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T14:27:31+00:00</t>
+    <t>2026-08-21T15:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.2</t>
+    <t>0.9.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T15:06:05+00:00</t>
+    <t>2026-08-21T16:05:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.3</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-21T16:05:47+00:00</t>
+    <t>2026-08-22T02:14:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T02:14:01+00:00</t>
+    <t>2026-08-22T04:25:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="50">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.10.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T04:25:10+00:00</t>
+    <t>2026-08-22T08:31:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -133,6 +133,12 @@
   </si>
   <si>
     <t>Waist Circumference at umbilicus by Tape measure</t>
+  </si>
+  <si>
+    <t>8281-8</t>
+  </si>
+  <si>
+    <t>Waist Circumference at umbilicus by US</t>
   </si>
   <si>
     <t>8480-6</t>
@@ -428,7 +434,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -509,18 +515,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>22</v>
+        <v>46</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>22</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>47</v>
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="2">
+        <v>48</v>
+      </c>
+      <c r="B12" t="s" s="2">
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.1</t>
+    <t>0.10.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T08:31:54+00:00</t>
+    <t>2026-08-22T14:05:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-VS-TWHAVitalSigns.xlsx
+++ b/ValueSet-VS-TWHAVitalSigns.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.2</t>
+    <t>0.10.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-22T14:05:28+00:00</t>
+    <t>2026-08-22T17:09:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
